--- a/src/attributions/attributions_ig_traj_208.xlsx
+++ b/src/attributions/attributions_ig_traj_208.xlsx
@@ -999,52 +999,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1189995096588194</v>
+        <v>-0.06295859478934329</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1533501581767698</v>
+        <v>0.0741924348241436</v>
       </c>
       <c r="E2" t="n">
-        <v>0.03820491265272186</v>
+        <v>0.02434955921536004</v>
       </c>
       <c r="F2" t="n">
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.03571577674372652</v>
+        <v>-0.0204058345755591</v>
       </c>
       <c r="L2" t="n">
         <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1004551707917509</v>
+        <v>0.07152410398532293</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01494109129065107</v>
+        <v>0.02640537612868033</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
         <v>-0</v>
@@ -1056,49 +1056,49 @@
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.09768496224987923</v>
+        <v>-0.05128180563276479</v>
       </c>
       <c r="U2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.04728553958601885</v>
+        <v>-0.0003536667513897818</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.04806758180207529</v>
+        <v>-0.00721986461613604</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA2" t="n">
         <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.1202645148627848</v>
+        <v>0.03111563566056744</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.01362974337732151</v>
+        <v>0.06906697854993603</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.008687117232680907</v>
+        <v>-0.009023753900038498</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
@@ -1107,184 +1107,184 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.03214680491862989</v>
+        <v>-0.05754417656568609</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.02310554055686026</v>
+        <v>-0.007703233991215041</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.06907203566315015</v>
+        <v>-0.09119985830630636</v>
       </c>
       <c r="AP2" t="n">
         <v>-0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>-0.1203915856580025</v>
+        <v>-0.1318854596356269</v>
       </c>
       <c r="AV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.09868566830804834</v>
+        <v>0.1246986616433613</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.03729292019893218</v>
+        <v>0.002036756751931715</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC2" t="n">
         <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.1888250193413885</v>
+        <v>0.05777939951929503</v>
       </c>
       <c r="BE2" t="n">
         <v>-0</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.1656516452178944</v>
+        <v>0.03714047934830029</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.05719822658356401</v>
+        <v>0.07485125353312881</v>
       </c>
       <c r="BH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
         <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM2" t="n">
-        <v>-0.02448970945267435</v>
+        <v>0.08426123784733619</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.01438380895761552</v>
+        <v>0.02867166496825108</v>
       </c>
       <c r="BP2" t="n">
-        <v>-0.08502503212953662</v>
+        <v>-0.01946399511313551</v>
       </c>
       <c r="BQ2" t="n">
         <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU2" t="n">
         <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0.1019770477678633</v>
+        <v>-0.165096469887962</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.07614478012646478</v>
+        <v>0.05217943745484466</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.004813751217620805</v>
+        <v>-0.005611388636149066</v>
       </c>
       <c r="BZ2" t="n">
         <v>-0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC2" t="n">
         <v>-0</v>
       </c>
       <c r="CD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>0.07181806879840889</v>
+        <v>0.08894791673630471</v>
       </c>
       <c r="CF2" t="n">
         <v>0</v>
       </c>
       <c r="CG2" t="n">
-        <v>-0.05939357944068038</v>
+        <v>-0.0454276532195769</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.002134876875353554</v>
+        <v>0.004712500430459856</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.00777862739710569</v>
+        <v>-0.006790637764043703</v>
       </c>
       <c r="CO2" t="n">
         <v>0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-8.673536639201127e-05</v>
+        <v>-0.005330700983187039</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.003417459931002382</v>
+        <v>-3.782617830364519e-06</v>
       </c>
       <c r="CR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS2" t="n">
         <v>0</v>
@@ -1296,76 +1296,76 @@
         <v>0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW2" t="n">
-        <v>0.08656081340624457</v>
+        <v>0.1047111321581097</v>
       </c>
       <c r="CX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY2" t="n">
-        <v>-0.07078009355897316</v>
+        <v>-0.05402569299780312</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.01171922853342548</v>
+        <v>-0.01818199172757546</v>
       </c>
       <c r="DA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE2" t="n">
         <v>-0</v>
       </c>
       <c r="DF2" t="n">
-        <v>0.2236384191468252</v>
+        <v>0.08973439324740611</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.01619321061349325</v>
+        <v>-0.01551335302342188</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.0592518533215597</v>
+        <v>0.05809903802532908</v>
       </c>
       <c r="DJ2" t="n">
         <v>0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>-0.1245951961150732</v>
+        <v>-0.05512213868193452</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.002334157125151816</v>
+        <v>-0.02768519293401746</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.0382412123797617</v>
+        <v>-0.0379908287889898</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>0</v>
@@ -1380,151 +1380,151 @@
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>0.0571732168949793</v>
+        <v>-0.00483960765683501</v>
       </c>
       <c r="DY2" t="n">
         <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.07302990326615932</v>
+        <v>-0.01900491941594758</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.1230961135104395</v>
+        <v>0.04337250269601859</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE2" t="n">
         <v>0</v>
       </c>
       <c r="EF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG2" t="n">
-        <v>0.01797319582196644</v>
+        <v>0.0685016845187625</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>-0.06071919253459453</v>
+        <v>-0.03998634558718449</v>
       </c>
       <c r="EJ2" t="n">
-        <v>-0.09393968745191536</v>
+        <v>-0.008479183189400021</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN2" t="n">
         <v>0</v>
       </c>
       <c r="EO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP2" t="n">
-        <v>0.07976059934589719</v>
+        <v>0.08957858154346179</v>
       </c>
       <c r="EQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER2" t="n">
-        <v>-0.01958304166622803</v>
+        <v>-0.02066781843811161</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.02170970851287473</v>
+        <v>0.01918844853060055</v>
       </c>
       <c r="ET2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY2" t="n">
-        <v>0.07844686024305111</v>
+        <v>0.110589172063372</v>
       </c>
       <c r="EZ2" t="n">
         <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>-0.05970301033590417</v>
+        <v>-0.06354910194607068</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.002547557475773452</v>
+        <v>0.005284124379967061</v>
       </c>
       <c r="FC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD2" t="n">
         <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG2" t="n">
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.05756498142159477</v>
+        <v>0.07621558376770068</v>
       </c>
       <c r="FI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.03505258702749752</v>
+        <v>0.04711617025944596</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.02244752241588263</v>
+        <v>-0.06393397773147819</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
       </c>
       <c r="FM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.02934327455945802</v>
+        <v>0.1046107596783603</v>
       </c>
       <c r="FR2" t="n">
         <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.0585068853275069</v>
+        <v>0.1088983684708395</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.1567168188581373</v>
+        <v>-0.02689072067872261</v>
       </c>
       <c r="FU2" t="n">
         <v>0</v>
@@ -1539,28 +1539,28 @@
         <v>-0</v>
       </c>
       <c r="FY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.02946147233315156</v>
+        <v>0.1084571643885577</v>
       </c>
       <c r="GA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.04163961950334544</v>
+        <v>-0.04741486197794829</v>
       </c>
       <c r="GC2" t="n">
         <v>-0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE2" t="n">
         <v>0</v>
       </c>
       <c r="GF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG2" t="n">
         <v>0</v>
@@ -1571,16 +1571,16 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3282621506258979</v>
+        <v>0.2004493004196418</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.07067469111754217</v>
+        <v>-0.06585799537327289</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.05519528114603867</v>
+        <v>-0.03397916144753687</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1598,16 +1598,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1729014843720989</v>
+        <v>0.1603087268280535</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02049498823427041</v>
+        <v>-0.02776020431384139</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.03059516725542099</v>
+        <v>-0.05499105042830636</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -1625,70 +1625,70 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1128268429334163</v>
+        <v>0.04726003183277439</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.05832513287221273</v>
+        <v>-0.04628233057184435</v>
       </c>
       <c r="W3" t="n">
-        <v>0.04439830741229778</v>
+        <v>-0.06993761942408713</v>
       </c>
       <c r="X3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
         <v>-0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.02779457650487974</v>
+        <v>-0.01605489028305601</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01083018934703295</v>
+        <v>-0.1433987081114612</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.023942770788668</v>
+        <v>-0.03107246918865566</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.04507584265991715</v>
+        <v>0.07896267108927911</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.05355310061271018</v>
+        <v>-0.09396542555542189</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.03378635328945417</v>
+        <v>0.06854766291008256</v>
       </c>
       <c r="AP3" t="n">
         <v>0</v>
@@ -1697,61 +1697,61 @@
         <v>-0</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.4817713100722847</v>
+        <v>0.2653206386718999</v>
       </c>
       <c r="AV3" t="n">
         <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.02059426733703729</v>
+        <v>-0.08452618435480866</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.06064063435997195</v>
+        <v>-0.2048679793810421</v>
       </c>
       <c r="AY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC3" t="n">
         <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.05618590033816762</v>
+        <v>0.01199179665659198</v>
       </c>
       <c r="BE3" t="n">
         <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.1495366466346227</v>
+        <v>-0.02343497825923763</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.1661584109804778</v>
+        <v>0.01489678818036355</v>
       </c>
       <c r="BH3" t="n">
         <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
@@ -1760,16 +1760,16 @@
         <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.09166139130090777</v>
+        <v>-0.004763480180668763</v>
       </c>
       <c r="BN3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.08722802718334731</v>
+        <v>0.03078907099990344</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.1003770477218975</v>
+        <v>0.06748507600065891</v>
       </c>
       <c r="BQ3" t="n">
         <v>-0</v>
@@ -1781,31 +1781,31 @@
         <v>-0</v>
       </c>
       <c r="BT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.2446100089885039</v>
+        <v>0.1536261997268009</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.01731787949323511</v>
+        <v>-0.1068093527997048</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.02140900968217718</v>
+        <v>-0.0780093314886554</v>
       </c>
       <c r="BZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
       </c>
       <c r="CB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
@@ -1814,70 +1814,70 @@
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.1199720790995365</v>
+        <v>-0.1212706697015103</v>
       </c>
       <c r="CF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.005454383253417465</v>
+        <v>0.09708176724627375</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.01254247660993785</v>
+        <v>0.02151574332718702</v>
       </c>
       <c r="CI3" t="n">
         <v>-0</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
         <v>0</v>
       </c>
       <c r="CL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM3" t="n">
         <v>0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.001612577650813489</v>
+        <v>-0.006669088983207515</v>
       </c>
       <c r="CO3" t="n">
         <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.004034987995798068</v>
+        <v>-0.008164415029705252</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.003965357549202132</v>
+        <v>0.001611083035675722</v>
       </c>
       <c r="CR3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
         <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW3" t="n">
-        <v>-0.1008374670215959</v>
+        <v>-0.1234466978868076</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.04842465952943773</v>
+        <v>0.1059894398495475</v>
       </c>
       <c r="CZ3" t="n">
-        <v>-0.02311254820948533</v>
+        <v>0.03445222985041064</v>
       </c>
       <c r="DA3" t="n">
         <v>0</v>
@@ -1889,22 +1889,22 @@
         <v>-0</v>
       </c>
       <c r="DD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.05076198593894102</v>
+        <v>-0.06847502432278563</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.07623925588711677</v>
+        <v>0.008795810317022458</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.01882772172872198</v>
+        <v>-0.04493827278490862</v>
       </c>
       <c r="DJ3" t="n">
         <v>-0</v>
@@ -1919,28 +1919,28 @@
         <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.09765554680361922</v>
+        <v>-0.06652357575043565</v>
       </c>
       <c r="DP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.02792547430473369</v>
+        <v>-0.03051067071971567</v>
       </c>
       <c r="DR3" t="n">
-        <v>-0.05806584383117854</v>
+        <v>-0.01510414350368985</v>
       </c>
       <c r="DS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT3" t="n">
         <v>-0</v>
       </c>
       <c r="DU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV3" t="n">
         <v>0</v>
@@ -1949,16 +1949,16 @@
         <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>-0.06141888835830987</v>
+        <v>-0.02469849497450822</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-0.03211834457639402</v>
+        <v>0.06660542711674662</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.003796832037543681</v>
+        <v>0.002621353421373754</v>
       </c>
       <c r="EB3" t="n">
         <v>-0</v>
@@ -1970,55 +1970,55 @@
         <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.08802192326429048</v>
+        <v>-0.07402472623988271</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.001654778752347651</v>
+        <v>0.06721210205497828</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.05531885967436971</v>
+        <v>0.04074862027480013</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN3" t="n">
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0.03013370523521062</v>
+        <v>-0.04864977591654251</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.03293569424628789</v>
+        <v>0.05548453473166658</v>
       </c>
       <c r="ES3" t="n">
-        <v>-0.007535749003071051</v>
+        <v>0.005641128469882966</v>
       </c>
       <c r="ET3" t="n">
         <v>-0</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV3" t="n">
         <v>0</v>
@@ -2030,43 +2030,43 @@
         <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>-0.09577218678658288</v>
+        <v>-0.1280990998266593</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.01979856230954029</v>
+        <v>0.1281598980787501</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.01435157516608045</v>
+        <v>0.01143367988645306</v>
       </c>
       <c r="FC3" t="n">
         <v>-0</v>
       </c>
       <c r="FD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG3" t="n">
         <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0.01376412416798826</v>
+        <v>0.1179109323749437</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.02310937950407561</v>
+        <v>0.08203507400032291</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.009795191954095058</v>
+        <v>0.02060023190729883</v>
       </c>
       <c r="FL3" t="n">
         <v>-0</v>
@@ -2078,28 +2078,28 @@
         <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.01684039270058593</v>
+        <v>0.03017668965135752</v>
       </c>
       <c r="FR3" t="n">
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.06859111605445233</v>
+        <v>0.1726049927927487</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.05867424185434746</v>
+        <v>-0.01634088554270449</v>
       </c>
       <c r="FU3" t="n">
         <v>-0</v>
       </c>
       <c r="FV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW3" t="n">
         <v>0</v>
@@ -2108,22 +2108,22 @@
         <v>0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.04379974577255098</v>
+        <v>-0.0485673450528489</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
-        <v>-0.05741347007397408</v>
+        <v>0.05965551884422356</v>
       </c>
       <c r="GC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE3" t="n">
         <v>-0</v>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1252741924572693</v>
+        <v>0.1632124471445986</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2149,10 +2149,10 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.02442850019046082</v>
+        <v>0.00448673100767258</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.06195940091863949</v>
+        <v>-0.1405178486851003</v>
       </c>
       <c r="G4" t="n">
         <v>-0</v>
@@ -2164,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07432019467939344</v>
+        <v>0.1556801241358239</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -2176,25 +2176,25 @@
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.006293762136260432</v>
+        <v>-0.06657488315872412</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.02981401254629272</v>
+        <v>-0.08648746121089732</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>-0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02454648284269994</v>
+        <v>0.09674304999413695</v>
       </c>
       <c r="U4" t="n">
         <v>-0</v>
@@ -2203,40 +2203,40 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.03972750031079016</v>
+        <v>-0.04486182542199562</v>
       </c>
       <c r="X4" t="n">
-        <v>0.008323500390494358</v>
+        <v>-0.05921466299176913</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.002229007468346449</v>
+        <v>-0.05425877301542621</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.006913792044371568</v>
+        <v>-0.1344332947845765</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.005413586804060021</v>
+        <v>0.03497152847157244</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2248,19 +2248,19 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.02633221778613722</v>
+        <v>0.1189958039356046</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.01296338150204399</v>
+        <v>0.02202988217107439</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.04187905734884135</v>
+        <v>-0.06613586007993913</v>
       </c>
       <c r="AQ4" t="n">
         <v>-0</v>
@@ -2272,184 +2272,184 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1442448904333173</v>
+        <v>0.4489686531924699</v>
       </c>
       <c r="AV4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.05793107057758094</v>
+        <v>-0.1627928129409353</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.07495670962056133</v>
+        <v>-0.1903208415894674</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.05767448850617522</v>
+        <v>-0.1215645048006569</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.02906618339284424</v>
+        <v>-0.02542154751950487</v>
       </c>
       <c r="BH4" t="n">
-        <v>-0.05076884527574192</v>
+        <v>-0.0524615634549004</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.04464983076964783</v>
+        <v>0.07602886484628618</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.02087101932238842</v>
+        <v>0.01916298004956639</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01486810779077125</v>
+        <v>0.0604240588757463</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.07671391141237444</v>
+        <v>0.2867970497083268</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.03719275841370218</v>
+        <v>-0.0636704612797053</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.02336855236693523</v>
+        <v>-0.1657984979924168</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
       </c>
       <c r="CB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.03710706565226674</v>
+        <v>-0.1173435549952998</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.00689452765706173</v>
+        <v>0.02848051193050123</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03548946732066772</v>
+        <v>0.08126521619707835</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>9.905483036298557e-05</v>
+        <v>-0.03022458887200518</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.001885875986163292</v>
+        <v>0.01719797964700586</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.001795254060951644</v>
+        <v>0.001511083024646814</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
         <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.03124201909351357</v>
+        <v>-0.1100971330218704</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
         <v>0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.00368760994463534</v>
+        <v>0.01638784070106911</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.04049728890235434</v>
+        <v>0.1037176719965333</v>
       </c>
       <c r="DB4" t="n">
         <v>0</v>
@@ -2464,19 +2464,19 @@
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.04119536163551066</v>
+        <v>-0.1550786644949953</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.06272896353173425</v>
+        <v>-0.008130180078008895</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.000993540312262385</v>
+        <v>0.03962771233517826</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,13 +2485,13 @@
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.01661400322171659</v>
+        <v>-0.09595749845580291</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
@@ -2500,16 +2500,16 @@
         <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.01207476079607537</v>
+        <v>0.02060868642870591</v>
       </c>
       <c r="DS4" t="n">
-        <v>-0.002415154066687166</v>
+        <v>0.1420902635663769</v>
       </c>
       <c r="DT4" t="n">
         <v>-0</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.03829024765850243</v>
+        <v>-0.05086052668661444</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.02130768646568726</v>
+        <v>0.09815785858163699</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.03191394859691989</v>
+        <v>0.04290778434405589</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2539,25 +2539,25 @@
         <v>0</v>
       </c>
       <c r="EE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF4" t="n">
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.02687247043137405</v>
+        <v>-0.03714732005701621</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.009398060924585035</v>
+        <v>-0.03545969631339964</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.03950571090450264</v>
+        <v>0.01558788468628112</v>
       </c>
       <c r="EL4" t="n">
         <v>-0</v>
@@ -2572,22 +2572,22 @@
         <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.02775340907505281</v>
+        <v>-0.04670337027550733</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.01419170093616628</v>
+        <v>-0.08222459110295705</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0.004494226890475793</v>
+        <v>0.04049039981027511</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.0326558970689864</v>
+        <v>-0.1267370074246406</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
@@ -2608,97 +2608,97 @@
         <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.001618542500429806</v>
+        <v>0.007907407138846606</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.04111796872556208</v>
+        <v>0.0968840555269483</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.02112262252595172</v>
+        <v>0.08426521734773426</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.01143210900121192</v>
+        <v>-0.0009423118285285838</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.0250582651477698</v>
+        <v>0.1100736786159468</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
       </c>
       <c r="FN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO4" t="n">
         <v>0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.01102773000475583</v>
+        <v>0.03027105872702069</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.03484134271576299</v>
+        <v>-0.05042609307010479</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.02693260878948061</v>
+        <v>-0.01150225666586404</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
       </c>
       <c r="FW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.003565491495719416</v>
+        <v>-0.02328993052472458</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
         <v>-0</v>
       </c>
       <c r="GC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.01830307506109398</v>
+        <v>0.1197843196169606</v>
       </c>
       <c r="GE4" t="n">
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG4" t="n">
         <v>-0</v>
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0949652096974922</v>
+        <v>0.2338299464740052</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -2718,10 +2718,10 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.03728630638338568</v>
+        <v>-0.04509231664001491</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0590392977445939</v>
+        <v>-0.1707884985751573</v>
       </c>
       <c r="G5" t="n">
         <v>-0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06267368577161539</v>
+        <v>0.2273744299413604</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -2745,64 +2745,64 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01981601960630219</v>
+        <v>-0.1086504224618332</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.01894069408257634</v>
+        <v>-0.06762757590701633</v>
       </c>
       <c r="P5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01120444826824325</v>
+        <v>0.1141575260924964</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01442674390834903</v>
+        <v>-0.1140481913883756</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01460814183037137</v>
+        <v>-0.02275613124219348</v>
       </c>
       <c r="Y5" t="n">
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.0006015177941063843</v>
+        <v>-0.01713502605619719</v>
       </c>
       <c r="AD5" t="n">
         <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.007546488730120055</v>
+        <v>-0.2211774542901143</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.007073630091902101</v>
+        <v>0.02910001897413275</v>
       </c>
       <c r="AH5" t="n">
         <v>-0</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.01020854347062319</v>
+        <v>0.07049475647209387</v>
       </c>
       <c r="AM5" t="n">
         <v>-0</v>
@@ -2826,10 +2826,10 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01616442117426703</v>
+        <v>-0.01641511141923313</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.01460132976577186</v>
+        <v>-0.01404229551518027</v>
       </c>
       <c r="AQ5" t="n">
         <v>-0</v>
@@ -2844,7 +2844,7 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1068862311197557</v>
+        <v>0.4476640170239211</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
@@ -2853,10 +2853,10 @@
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.03736026872051163</v>
+        <v>-0.2586389290941047</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.04847898986005111</v>
+        <v>-0.1976441069734446</v>
       </c>
       <c r="AZ5" t="n">
         <v>-0</v>
@@ -2865,13 +2865,13 @@
         <v>-0</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
         <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.03389401427689764</v>
+        <v>-0.02626423611976237</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
@@ -2880,25 +2880,25 @@
         <v>0</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.06464999640328285</v>
+        <v>-0.01710970607638079</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.05666062607004092</v>
+        <v>-0.1233991048267244</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.03586272656131363</v>
+        <v>0.05572717314712138</v>
       </c>
       <c r="BN5" t="n">
         <v>-0</v>
@@ -2907,13 +2907,13 @@
         <v>-0</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.02519317607495223</v>
+        <v>0.1104735294602847</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.0151388999010284</v>
+        <v>0.05695847275304409</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2922,10 +2922,10 @@
         <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.05342061989584779</v>
+        <v>0.2641089252985869</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
@@ -2934,10 +2934,10 @@
         <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.0179048286579471</v>
+        <v>-0.0894889901133529</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.009747843096237442</v>
+        <v>-0.1075473642992748</v>
       </c>
       <c r="CA5" t="n">
         <v>-0</v>
@@ -2946,40 +2946,40 @@
         <v>-0</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="n">
         <v>-0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.02636874105947959</v>
+        <v>-0.1157439778528707</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
         <v>-0</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.001975801502900745</v>
+        <v>0.03096071432938259</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.02604634371896382</v>
+        <v>0.09889540111489913</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>0</v>
       </c>
       <c r="CM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.001887142121853433</v>
+        <v>-0.03995428964213581</v>
       </c>
       <c r="CO5" t="n">
         <v>-0</v>
@@ -2988,106 +2988,106 @@
         <v>-0</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.003239020109405809</v>
+        <v>0.02517833621301701</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.005377598091282574</v>
+        <v>0.02960924848356328</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU5" t="n">
         <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.01916135139224375</v>
+        <v>-0.1177819078818701</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
         <v>0</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.006937739978479198</v>
+        <v>0.02602044776244401</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.02884377715882283</v>
+        <v>0.12470216859716</v>
       </c>
       <c r="DB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC5" t="n">
         <v>-0</v>
       </c>
       <c r="DD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.03234619531410638</v>
+        <v>-0.08519793161185196</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.03936533021144174</v>
+        <v>-0.1082763778619327</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.000197873080402129</v>
+        <v>0.02309856041663145</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN5" t="n">
         <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.005677214123200489</v>
+        <v>-0.007142735290714134</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.003862112331394705</v>
+        <v>-0.08191991177522359</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.003268016883474112</v>
+        <v>0.02381205136144847</v>
       </c>
       <c r="DT5" t="n">
         <v>-0</v>
       </c>
       <c r="DU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.02769429968492073</v>
+        <v>-0.07997335739372577</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
@@ -3096,10 +3096,10 @@
         <v>-0</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.01745060575821885</v>
+        <v>0.01549739038121717</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.02120898817590763</v>
+        <v>0.1138798663477836</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
@@ -3108,13 +3108,13 @@
         <v>0</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.0267120190186194</v>
+        <v>-0.03774774193007852</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
@@ -3123,13 +3123,13 @@
         <v>0</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.01339614754204236</v>
+        <v>0.009863117695689512</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.03071112427057209</v>
+        <v>0.03626563222257265</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM5" t="n">
         <v>-0</v>
@@ -3138,22 +3138,22 @@
         <v>0</v>
       </c>
       <c r="EO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.01244741457063447</v>
+        <v>-0.004591038836796635</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.01966083564541494</v>
+        <v>-0.0154083672741201</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.002215931375825109</v>
+        <v>0.09743636991160948</v>
       </c>
       <c r="EU5" t="n">
         <v>0</v>
@@ -3162,13 +3162,13 @@
         <v>0</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.01875397282933003</v>
+        <v>-0.1332567183756629</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
@@ -3177,43 +3177,43 @@
         <v>-0</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.00905219666370099</v>
+        <v>0.004831693490436905</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.03065847987327199</v>
+        <v>0.08934301982036819</v>
       </c>
       <c r="FD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG5" t="n">
         <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>-0.0133818155736513</v>
+        <v>0.1752332460799456</v>
       </c>
       <c r="FI5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ5" t="n">
         <v>-0</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.01530504313212281</v>
+        <v>-0.08254258006054098</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.01367942837739076</v>
+        <v>0.1022311313672397</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
@@ -3222,55 +3222,55 @@
         <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.005973686642064843</v>
+        <v>0.05021221545028814</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
         <v>-0</v>
       </c>
       <c r="FT5" t="n">
-        <v>-0.02268208300126317</v>
+        <v>-0.07408345872905736</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.001941105247428274</v>
+        <v>-0.05842819644037946</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
       </c>
       <c r="FW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.004506187631375721</v>
+        <v>-0.02997205847522474</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
         <v>-0</v>
       </c>
       <c r="GC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0.004650591706309626</v>
+        <v>0.1195966198131814</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
       </c>
       <c r="GF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -3278,22 +3278,22 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2664677566275784</v>
+        <v>0.2659883391664584</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.06687557076772582</v>
+        <v>-0.1272951381303252</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02166332157013325</v>
+        <v>-0.03481434253039722</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>-0</v>
@@ -3305,22 +3305,22 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1575619066178652</v>
+        <v>0.2196117197166859</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.01739184430242398</v>
+        <v>-0.0376211978533209</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0234216242837453</v>
+        <v>-0.0620333923211602</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3332,70 +3332,70 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.09193335737946468</v>
+        <v>0.035189556889292</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.008577422441560982</v>
+        <v>-0.01589440394567231</v>
       </c>
       <c r="W6" t="n">
-        <v>0.07137315371615988</v>
+        <v>-0.09537216430272602</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1288799954084406</v>
+        <v>-0.03576099385886026</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.05543314083658589</v>
+        <v>-0.1319013720924937</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.0639881317689983</v>
+        <v>-0.08090312788392381</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0191668443617124</v>
+        <v>0.1042656904932859</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.07465173304347805</v>
+        <v>-0.0926604225574602</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.03950184855812367</v>
+        <v>-0.001404017820782306</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -3404,7 +3404,7 @@
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
@@ -3413,16 +3413,16 @@
         <v>-0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.3402261065497438</v>
+        <v>0.2863772289109042</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.02282106211632072</v>
+        <v>-0.2255690013232935</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1402708353076748</v>
+        <v>-0.3547201339361166</v>
       </c>
       <c r="AY6" t="n">
         <v>-0</v>
@@ -3431,25 +3431,25 @@
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.02317112199111455</v>
+        <v>-0.01905596483494369</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.05263425754150079</v>
+        <v>-0.02652689873448098</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1742390220434095</v>
+        <v>0.05988981325764738</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,157 +3467,157 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.02846254590458597</v>
+        <v>0.0270643492218086</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.102396423490388</v>
+        <v>0.08887087220171265</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.09760688781120505</v>
+        <v>-0.004970718508531545</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS6" t="n">
         <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1955332599769841</v>
+        <v>0.2210062462574209</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.009760102215575569</v>
+        <v>-0.1384691001890866</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.06368245706280408</v>
+        <v>-0.1204806633881428</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.08647086017442367</v>
+        <v>-0.124059919011113</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.01847732359235087</v>
+        <v>0.1633931115322596</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.003477414591038768</v>
+        <v>0.01364696975885646</v>
       </c>
       <c r="CI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.01236449922424798</v>
+        <v>-0.02304745055207896</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.01366777652518273</v>
+        <v>0.02994393267657082</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.0160037832829557</v>
+        <v>0.03179595403895032</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>0</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU6" t="n">
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.07297756348712434</v>
+        <v>-0.1187011804529361</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.04121773983686554</v>
+        <v>0.1712250052492665</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.002979086157617199</v>
+        <v>0.02271660399968835</v>
       </c>
       <c r="DA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.008189238239191465</v>
+        <v>-0.08124773712572772</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.0006852416009869649</v>
+        <v>-0.01166959948018935</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.005680473924477154</v>
+        <v>-0.1025278947772101</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
@@ -3626,25 +3626,25 @@
         <v>0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.05631915012161703</v>
+        <v>-0.05275807236684518</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.05904615088694184</v>
+        <v>0.07657556559997801</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.06804997619157721</v>
+        <v>-0.02664149113382003</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU6" t="n">
         <v>-0</v>
@@ -3653,19 +3653,19 @@
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.008222784841514215</v>
+        <v>0.02967950601888789</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.02412267923838689</v>
+        <v>0.06797828213051996</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.007746247568073735</v>
+        <v>0.007061298229622902</v>
       </c>
       <c r="EB6" t="n">
         <v>0</v>
@@ -3674,58 +3674,58 @@
         <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.05374992536739786</v>
+        <v>-0.07728168177128913</v>
       </c>
       <c r="EH6" t="n">
         <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.02801380733983705</v>
+        <v>0.1267542946298355</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.09216251684078954</v>
+        <v>0.02311010627353205</v>
       </c>
       <c r="EK6" t="n">
         <v>0</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.07881720500327108</v>
+        <v>-0.07138658397270184</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>-0.09619705771774714</v>
+        <v>-0.08455778459805284</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01231212388575484</v>
+        <v>-0.03447984910770334</v>
       </c>
       <c r="ET6" t="n">
         <v>-0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3734,25 +3734,25 @@
         <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.076543493233383</v>
+        <v>-0.1370737074003537</v>
       </c>
       <c r="EZ6" t="n">
         <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.02745528439441419</v>
+        <v>0.1887387261815388</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.008365943726777019</v>
+        <v>0.004103803092661768</v>
       </c>
       <c r="FC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
@@ -3764,49 +3764,49 @@
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.006700438497129123</v>
+        <v>0.1500201919245805</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.05307044812016626</v>
+        <v>0.1493749458125978</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.02047170078642161</v>
+        <v>-0.005401265823235972</v>
       </c>
       <c r="FL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.004647956637920265</v>
+        <v>0.0582271933402738</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.07662880175140503</v>
+        <v>0.2072390207026886</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0300889572119485</v>
+        <v>-0.04490619998110154</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
         <v>0</v>
@@ -3815,31 +3815,31 @@
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.03306653617143729</v>
+        <v>-0.04436569333704481</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.02599061361645779</v>
+        <v>0.11581427123139</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.1614021059590444</v>
+        <v>0.2637495184629943</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04219809942237988</v>
+        <v>-0.002457862719624822</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1079967222197808</v>
+        <v>-0.2656843170324504</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
@@ -3868,13 +3868,13 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1102659777608607</v>
+        <v>0.2659387298429532</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,13 +3883,13 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.01007459886424139</v>
+        <v>-0.1069637076815455</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.04660032298544525</v>
+        <v>-0.1726764768529153</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-0</v>
@@ -3898,10 +3898,10 @@
         <v>-0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03145484414712869</v>
+        <v>0.1095261118129487</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,37 +3910,37 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.02748880627428892</v>
+        <v>-0.07347675502248895</v>
       </c>
       <c r="X7" t="n">
-        <v>6.687332830135055e-05</v>
+        <v>-0.08459743967487124</v>
       </c>
       <c r="Y7" t="n">
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.003045064894926972</v>
+        <v>-0.06724416215739645</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.002934934990847403</v>
+        <v>-0.183663939822314</v>
       </c>
       <c r="AG7" t="n">
-        <v>-0.01141117984401613</v>
+        <v>0.04378586336648519</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -3955,22 +3955,22 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02630078945839943</v>
+        <v>0.1298878959981632</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.009227050241081072</v>
+        <v>-0.01137875036433147</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.05160836073309838</v>
+        <v>-0.08500081501922691</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
         <v>-0</v>
@@ -3979,37 +3979,37 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1499935728907132</v>
+        <v>0.5208460645850533</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.0360768711567828</v>
+        <v>-0.2355000447279393</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.1144330747275005</v>
+        <v>-0.3084199643160916</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.05051923695949444</v>
+        <v>-0.1184922017789129</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,106 +4018,106 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0430234418886324</v>
+        <v>0.0003412604038698286</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.05013006106580862</v>
+        <v>-0.07465916679442706</v>
       </c>
       <c r="BI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ7" t="n">
         <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.04514426184019323</v>
+        <v>0.09367999786699899</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.02377076728441082</v>
+        <v>0.06827523255152769</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.005634465044272521</v>
+        <v>0.07131549978338203</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.08779114063483127</v>
+        <v>0.29397774409549</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.02226653557702884</v>
+        <v>-0.09112174789603736</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.0337682231030756</v>
+        <v>-0.172301179900803</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>-0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.04164081896780822</v>
+        <v>-0.1402434813865686</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.002601319383258837</v>
+        <v>0.04328882329170262</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0374618592202823</v>
+        <v>0.09682268742658043</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.0005985778091141983</v>
+        <v>-0.06270866466852146</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
@@ -4126,37 +4126,37 @@
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0002034027407754048</v>
+        <v>0.06233138290134799</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.008772969344912052</v>
+        <v>-0.003953584228258172</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
         <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.03694744982586466</v>
+        <v>-0.1306636231670717</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.007457222889347062</v>
+        <v>0.02687725087543552</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.04104813592563297</v>
+        <v>0.1304277815868528</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
@@ -4171,19 +4171,19 @@
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.006254489742205234</v>
+        <v>0.02385265714821831</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.0542942140211693</v>
+        <v>-0.01315168923964517</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.002370282113173969</v>
+        <v>0.0424047212425212</v>
       </c>
       <c r="DK7" t="n">
         <v>0</v>
@@ -4192,13 +4192,13 @@
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.01863149912064417</v>
+        <v>-0.1017613423658512</v>
       </c>
       <c r="DP7" t="n">
         <v>0</v>
@@ -4207,25 +4207,25 @@
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.01587481718419863</v>
+        <v>0.01490040182650943</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0104301240679308</v>
+        <v>0.1481534976591358</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.04859353726203718</v>
+        <v>-0.09227825152087821</v>
       </c>
       <c r="DY7" t="n">
         <v>-0</v>
@@ -4234,10 +4234,10 @@
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.03011983511169006</v>
+        <v>0.1232194832036374</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.01615980642009766</v>
+        <v>0.05413045163739517</v>
       </c>
       <c r="EC7" t="n">
         <v>0</v>
@@ -4246,25 +4246,25 @@
         <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0338345813974287</v>
+        <v>-0.02202738808044126</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
         <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.01346392181100476</v>
+        <v>-0.03344990944914124</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.03722704469168663</v>
+        <v>0.01592700201458891</v>
       </c>
       <c r="EL7" t="n">
         <v>-0</v>
@@ -4273,13 +4273,13 @@
         <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.03490093756772508</v>
+        <v>-0.05666610493631818</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,13 +4288,13 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>-0.00491364843081376</v>
+        <v>-0.090470787736391</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.001223714918450935</v>
+        <v>0.02518888585202857</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.03708898914753966</v>
+        <v>-0.1549635250126028</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,25 +4315,25 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.008857912294380644</v>
+        <v>0.0183315452317366</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.03881385243021201</v>
+        <v>0.1182343854743128</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.02291612023320728</v>
+        <v>0.09640976236477264</v>
       </c>
       <c r="FI7" t="n">
         <v>0</v>
@@ -4342,25 +4342,25 @@
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.01166114376161707</v>
+        <v>-0.01078144944544075</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.03046286514715778</v>
+        <v>0.1415866608202401</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.0003855999512519972</v>
+        <v>0.01747621690031755</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,37 +4369,37 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.02341091064655549</v>
+        <v>-0.062407361824199</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.02148670067886784</v>
+        <v>0.001239998357270747</v>
       </c>
       <c r="FV7" t="n">
         <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.005843258119904952</v>
+        <v>-0.02050492634539401</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.01771456769903796</v>
+        <v>0.1470003245352741</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
@@ -4416,46 +4416,46 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2544148304269785</v>
+        <v>0.2332591897009052</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.08090334743257342</v>
+        <v>-0.09864340130265382</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.06348880322656947</v>
+        <v>0.007840781256374265</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.03082242257387469</v>
+        <v>-0.1017389469751471</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
         <v>-0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1705771301089562</v>
+        <v>0.2492836896340757</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03084949665462829</v>
+        <v>-0.06477787522459365</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.03916080046217604</v>
+        <v>-0.0541689393651722</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0182647761061194</v>
+        <v>-0.04861664327580144</v>
       </c>
       <c r="P8" t="n">
         <v>-0</v>
@@ -4470,133 +4470,133 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.07247514678859363</v>
+        <v>0.1095740626602643</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.02259412542925097</v>
+        <v>-0.07820349153836074</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03390489275307827</v>
+        <v>-0.09582292809266534</v>
       </c>
       <c r="X8" t="n">
-        <v>0.01156401618900172</v>
+        <v>-0.05637678640371475</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0519272988658465</v>
+        <v>-0.05813851907592984</v>
       </c>
       <c r="AD8" t="n">
         <v>-0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.01645288554819481</v>
+        <v>-0.1291974820052072</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.01037722191608653</v>
+        <v>-0.02486117274958804</v>
       </c>
       <c r="AG8" t="n">
-        <v>-0.01454376237645992</v>
+        <v>0.04677254682411453</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.01754840614655391</v>
+        <v>0.0718815098739042</v>
       </c>
       <c r="AM8" t="n">
         <v>-0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.05441880247909799</v>
+        <v>-0.06523525442344005</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.05663756222168156</v>
+        <v>0.0303641127180444</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0.03143019210083094</v>
+        <v>-0.03519283786603839</v>
       </c>
       <c r="AQ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.2787018848906869</v>
+        <v>0.3358627934093814</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.03738360019611399</v>
+        <v>-0.1448402172907368</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.02929327527534451</v>
+        <v>-0.1807854403723988</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.02863277868660639</v>
+        <v>-0.1500192683490497</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.03650298200421864</v>
+        <v>-0.03876236742803581</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.06193345691294583</v>
+        <v>-0.06577944652960477</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1060179102568253</v>
+        <v>0.002537250875248778</v>
       </c>
       <c r="BH8" t="n">
-        <v>-0.05137240778747439</v>
+        <v>-0.09499744395853608</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
@@ -4605,52 +4605,52 @@
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.05932261603251734</v>
+        <v>0.03152415794907783</v>
       </c>
       <c r="BN8" t="n">
         <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.04508413113331623</v>
+        <v>0.07135233838441152</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.094391374834789</v>
+        <v>0.01128143761261934</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0.03433326477452107</v>
+        <v>0.00847904956641198</v>
       </c>
       <c r="BR8" t="n">
         <v>0</v>
       </c>
       <c r="BS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1230887088480027</v>
+        <v>0.1822156263299028</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>-0.0003152629878677693</v>
+        <v>-0.08484471380544931</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.01546761993453965</v>
+        <v>-0.0619001528438419</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.01300657820283278</v>
+        <v>-0.120914052824565</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
         <v>-0</v>
@@ -4659,22 +4659,22 @@
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.06474389223451436</v>
+        <v>-0.0829146340895735</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.01030704245457573</v>
+        <v>0.08520005595206614</v>
       </c>
       <c r="CH8" t="n">
-        <v>-0.0004332358752207977</v>
+        <v>-0.004785292166055136</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.02393477941510408</v>
+        <v>0.03815390680603389</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
@@ -4686,49 +4686,49 @@
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.002434142779234652</v>
+        <v>-0.01768083925895379</v>
       </c>
       <c r="CO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.02065829896247383</v>
+        <v>0.07939146598219299</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.0234808539883039</v>
+        <v>0.04281661574387435</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0.008576863631374715</v>
+        <v>0.01491291707202384</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.0520136138771025</v>
+        <v>-0.09024721154205971</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.02975399520487267</v>
+        <v>0.1031189129628287</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.002781641474466557</v>
+        <v>0.001058522354058133</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.02345080712251381</v>
+        <v>0.06411229122074162</v>
       </c>
       <c r="DB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC8" t="n">
         <v>-0</v>
@@ -4740,19 +4740,19 @@
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.02126049947314931</v>
+        <v>-0.05005198045523417</v>
       </c>
       <c r="DG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.04586223475190544</v>
+        <v>0.02148734244723902</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.003515885707480859</v>
+        <v>0.008721301693020354</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.01155736460264912</v>
+        <v>0.02225649153489791</v>
       </c>
       <c r="DK8" t="n">
         <v>-0</v>
@@ -4761,31 +4761,31 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.007481895029152985</v>
+        <v>0.003259219291390377</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.03647467734874746</v>
+        <v>0.01630937828527771</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.01213211435547958</v>
+        <v>-0.09903329835715272</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.02191089508513551</v>
+        <v>-0.008488403128685415</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
       </c>
       <c r="DU8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
@@ -4794,76 +4794,76 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.03110354056448166</v>
+        <v>-0.03152720806278359</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.01422892835801701</v>
+        <v>0.07535053591118444</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.006850586820937729</v>
+        <v>0.002853605590323939</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.03109727963270507</v>
+        <v>-0.03283278132973835</v>
       </c>
       <c r="EC8" t="n">
         <v>0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
         <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.07559501792916618</v>
+        <v>-0.07669915388376217</v>
       </c>
       <c r="EH8" t="n">
         <v>-0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.03133453656266989</v>
+        <v>0.08848129418591792</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.05036814724132325</v>
+        <v>0.01756881906380279</v>
       </c>
       <c r="EK8" t="n">
-        <v>0.01740575306078377</v>
+        <v>-0.03547673785525542</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM8" t="n">
         <v>-0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.04941886702989354</v>
+        <v>-0.03276061649805676</v>
       </c>
       <c r="EQ8" t="n">
         <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.024730117293911</v>
+        <v>0.05780624883457301</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.01927854337588088</v>
+        <v>0.01990338925930819</v>
       </c>
       <c r="ET8" t="n">
-        <v>0.04276023830144388</v>
+        <v>0.07111920748195157</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,22 +4875,22 @@
         <v>0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.05178251800645158</v>
+        <v>-0.09378231280059415</v>
       </c>
       <c r="EZ8" t="n">
         <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.01237272072918067</v>
+        <v>0.120409543093001</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.00867046598557298</v>
+        <v>-0.01626768672736428</v>
       </c>
       <c r="FC8" t="n">
-        <v>0.02857985326345245</v>
+        <v>0.05165170828399814</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE8" t="n">
         <v>0</v>
@@ -4899,79 +4899,79 @@
         <v>0</v>
       </c>
       <c r="FG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02475879511597032</v>
+        <v>0.0905046499516995</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.03219089424031935</v>
+        <v>0.08140453745612544</v>
       </c>
       <c r="FK8" t="n">
-        <v>0.004574312554070849</v>
+        <v>0.009148892699921862</v>
       </c>
       <c r="FL8" t="n">
-        <v>-0.01453576872992135</v>
+        <v>0.1311169282637053</v>
       </c>
       <c r="FM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
         <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.003527819883250769</v>
+        <v>0.01234648392124316</v>
       </c>
       <c r="FR8" t="n">
         <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.01162157996649836</v>
+        <v>0.1447325640896089</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.02099817182313915</v>
+        <v>-0.03871890756369512</v>
       </c>
       <c r="FU8" t="n">
-        <v>0.02062933021221709</v>
+        <v>0.0003131011453038783</v>
       </c>
       <c r="FV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.01613676611227705</v>
+        <v>-0.02917821787543803</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.04654164419198333</v>
+        <v>0.03408992115822212</v>
       </c>
       <c r="GC8" t="n">
         <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0.02467008542999251</v>
+        <v>0.06898684473354669</v>
       </c>
       <c r="GE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF8" t="n">
         <v>0</v>
@@ -4985,46 +4985,46 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.237896476817857</v>
+        <v>0.2375468551721085</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0436093735245818</v>
+        <v>-0.07880921409263947</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03038822293661352</v>
+        <v>-0.02042596060087538</v>
       </c>
       <c r="F9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1481732776272314</v>
+        <v>0.2511321931860082</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.03781628543730666</v>
+        <v>-0.07316806844272514</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0243820948688811</v>
+        <v>-0.0578316264851264</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -5039,19 +5039,19 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06073600166415747</v>
+        <v>0.06350122554956884</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>0.013108936085467</v>
+        <v>-0.02582187775164011</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06282373794721195</v>
+        <v>-0.0443496453025258</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
@@ -5060,49 +5060,49 @@
         <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.07110652727877237</v>
+        <v>-0.01455804451733786</v>
       </c>
       <c r="AD9" t="n">
         <v>-0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.02623933742767117</v>
+        <v>-0.1021752197853863</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.02361438632614427</v>
+        <v>-0.003945884089188537</v>
       </c>
       <c r="AG9" t="n">
         <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.02063627480564742</v>
+        <v>0.06825637674071998</v>
       </c>
       <c r="AM9" t="n">
         <v>-0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.05842278690262018</v>
+        <v>-0.06216982623005346</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.04815023385989389</v>
+        <v>0.08078127538378665</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5111,61 +5111,61 @@
         <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2493982048527771</v>
+        <v>0.2193765166036938</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.0373742836404579</v>
+        <v>-0.05220522989602581</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.09738027813142754</v>
+        <v>-0.1217862474811083</v>
       </c>
       <c r="AY9" t="n">
         <v>-0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
       </c>
       <c r="BC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.01096617176364721</v>
+        <v>0.002112133877559941</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.08998409461166423</v>
+        <v>-0.02741741502310599</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.07987468970940774</v>
+        <v>-0.02321422665123914</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
       </c>
       <c r="BI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,16 +5174,16 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.05257468434215243</v>
+        <v>-0.01749651062723939</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.03605957888914056</v>
+        <v>0.01862826704594087</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1518119628043807</v>
+        <v>0.06540539624522122</v>
       </c>
       <c r="BQ9" t="n">
         <v>-0</v>
@@ -5195,82 +5195,82 @@
         <v>-0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1254533628935607</v>
+        <v>0.1491580291654015</v>
       </c>
       <c r="BW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.04334707789584909</v>
+        <v>-0.04702748738984291</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0486730181786706</v>
+        <v>-0.02422883262042121</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.06624784033914478</v>
+        <v>-0.09481349289989927</v>
       </c>
       <c r="CF9" t="n">
         <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>-0.007135762293731935</v>
+        <v>0.06698812080441648</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.004683987820704888</v>
+        <v>0.0001169462728384282</v>
       </c>
       <c r="CI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.004672098393066564</v>
+        <v>-0.03679635643026079</v>
       </c>
       <c r="CO9" t="n">
         <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.0328052963582822</v>
+        <v>0.09482950939892033</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.03981975345119936</v>
+        <v>0.01073621032965499</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT9" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
         <v>-0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.04940858106735858</v>
+        <v>-0.0930902853824766</v>
       </c>
       <c r="CX9" t="n">
         <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.01094439048801722</v>
+        <v>0.07710751814620391</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.006561666691859244</v>
+        <v>0.006730966462998131</v>
       </c>
       <c r="DA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
@@ -5309,16 +5309,16 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.02363498809162607</v>
+        <v>-0.0421603666518368</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01377598302955775</v>
+        <v>0.01173788038627751</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02003233016544772</v>
+        <v>-0.05220595662868791</v>
       </c>
       <c r="DJ9" t="n">
         <v>-0</v>
@@ -5330,22 +5330,22 @@
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.03103811151677779</v>
+        <v>-0.04213903620217745</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.05725975771608918</v>
+        <v>-0.0677509423576199</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.036431311288004</v>
+        <v>-0.04842059248112475</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -5354,82 +5354,82 @@
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.03536288546140816</v>
+        <v>-0.03258859778663346</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.01318772188686606</v>
+        <v>0.03923120174070775</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.02492397921502441</v>
+        <v>-0.005533430174367111</v>
       </c>
       <c r="EB9" t="n">
         <v>0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.07119682298795864</v>
+        <v>-0.07052609940960772</v>
       </c>
       <c r="EH9" t="n">
         <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.009817477845721373</v>
+        <v>0.04293820716732997</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0546578867457018</v>
+        <v>0.03860856098113115</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.02772870767862578</v>
+        <v>-0.01833554341609035</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.02722572689726733</v>
+        <v>-0.003146895070748316</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.02496594117444132</v>
+        <v>-0.01005097624578049</v>
       </c>
       <c r="ET9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU9" t="n">
         <v>0</v>
@@ -5438,25 +5438,25 @@
         <v>0</v>
       </c>
       <c r="EW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.05004109852386204</v>
+        <v>-0.09827363472842045</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>-0.0101473473051773</v>
+        <v>0.09148468284742103</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.009464303246608659</v>
+        <v>-0.01630602038741265</v>
       </c>
       <c r="FC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD9" t="n">
         <v>0</v>
@@ -5471,16 +5471,16 @@
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.01961020720907754</v>
+        <v>0.08808124505104803</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.01170434954569517</v>
+        <v>0.06937769681474022</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.02795329823030964</v>
+        <v>0.008683518761013538</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
@@ -5492,69 +5492,69 @@
         <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.001265778513684855</v>
+        <v>0.001186631988236873</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.02191412973035731</v>
+        <v>0.08913444895733157</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.0063335908818302</v>
+        <v>-0.0159241203260644</v>
       </c>
       <c r="FU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV9" t="n">
         <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.006831559721899597</v>
+        <v>-0.07241621261424752</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.07284799265092745</v>
+        <v>0.02940673092952866</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
         <v>-0</v>
       </c>
       <c r="GE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF9" t="n">
         <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.3181714060222989</v>
+        <v>0.3899218363818895</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,10 +5563,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.06921121801587908</v>
+        <v>0.009864005106452144</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2200405188573906</v>
+        <v>-0.332320167918203</v>
       </c>
       <c r="G10" t="n">
         <v>-0</v>
@@ -5575,13 +5575,13 @@
         <v>-0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2662765277523556</v>
+        <v>0.4794613019630724</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,25 +5590,25 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.009229229026850756</v>
+        <v>-0.06487507796783731</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1841052981580193</v>
+        <v>-0.3837595987118073</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.03174655778379745</v>
+        <v>0.1524788066617326</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -5617,52 +5617,52 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.02973079441249544</v>
+        <v>-0.1050469918989501</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.02237286862707015</v>
+        <v>-0.09243020145338293</v>
       </c>
       <c r="Y10" t="n">
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB10" t="n">
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.00789349131374752</v>
+        <v>-0.02672949758960518</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.02687583523725001</v>
+        <v>-0.2971040128624429</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.008286817877531142</v>
+        <v>0.1072414605469334</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI10" t="n">
         <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.05220196105579709</v>
+        <v>0.1279150685762198</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
@@ -5671,13 +5671,13 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.00347618845568394</v>
+        <v>-0.07383181352715731</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.06781739298557067</v>
+        <v>-0.09708679171043744</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
@@ -5686,37 +5686,37 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.2540688296376737</v>
+        <v>0.6917520010315351</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.02325799582030611</v>
+        <v>-0.3048745566660288</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.09869836344767019</v>
+        <v>-0.2147052512333451</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.06601382469865869</v>
+        <v>-0.1247991796875535</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,25 +5725,25 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.06550797205784568</v>
+        <v>-0.01827485697616791</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.09328528101738426</v>
+        <v>-0.03027547166941766</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.05522049086429748</v>
+        <v>0.1283099168724686</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,37 +5752,37 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02332168532923288</v>
+        <v>0.08683014695170015</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.003145393272133907</v>
+        <v>0.04034326622823224</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.1356888450955493</v>
+        <v>0.3834853760895292</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.02857721706062801</v>
+        <v>-0.03463490205451796</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.05928649705528599</v>
+        <v>-0.1988713882680811</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5791,121 +5791,121 @@
         <v>-0</v>
       </c>
       <c r="CC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD10" t="n">
         <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.07046015812946713</v>
+        <v>-0.1604073552160244</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.004369425689960977</v>
+        <v>0.03722790244158839</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.05098138898492927</v>
+        <v>0.1126219337476933</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
         <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.002705946854953744</v>
+        <v>-0.1424752382853526</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.01107657445476865</v>
+        <v>0.1161796301395308</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.05462684939216569</v>
+        <v>0.03278900750350976</v>
       </c>
       <c r="CS10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV10" t="n">
         <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.06408456696946062</v>
+        <v>-0.1498471828305221</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.005020275297892534</v>
+        <v>0.0200220102157924</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.05047307577611771</v>
+        <v>0.1473617720650596</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
         <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.04058528403830124</v>
+        <v>-0.1137800708607326</v>
       </c>
       <c r="DG10" t="n">
         <v>0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.07237179471718447</v>
+        <v>-0.06973347219580774</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.06468112311974526</v>
+        <v>0.0992109559954511</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
         <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.02334669534832587</v>
+        <v>-0.08245035170878011</v>
       </c>
       <c r="DP10" t="n">
         <v>0</v>
@@ -5914,64 +5914,64 @@
         <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.02248313688735628</v>
+        <v>0.0002822193423697158</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.01926656340829383</v>
+        <v>0.1197042039140182</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.06729577112161042</v>
+        <v>-0.09235534713464198</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.02003493381474684</v>
+        <v>0.005146953154986625</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.04051045600176061</v>
+        <v>0.0317553173439139</v>
       </c>
       <c r="EC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.07345831806276373</v>
+        <v>-0.03036703372010341</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
         <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.02928797524045762</v>
+        <v>-0.02072677195535769</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.02975832967714346</v>
+        <v>0.02658450988318832</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
@@ -5980,28 +5980,28 @@
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.06063270402598368</v>
+        <v>-0.0649198049898569</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.0292228082335334</v>
+        <v>-0.08217413104774833</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0.005057622525602738</v>
+        <v>-0.0250771500370048</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
@@ -6013,46 +6013,46 @@
         <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.06449076470142905</v>
+        <v>-0.1813151343123715</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA10" t="n">
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.003430011345034501</v>
+        <v>-0.003995121266751043</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.04994541051334974</v>
+        <v>0.1285816669522933</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.03918592546325897</v>
+        <v>0.1130654240567854</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.004166144048948783</v>
+        <v>-0.05807015726348473</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.03314108608817785</v>
+        <v>0.1756622865518914</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
@@ -6064,49 +6064,49 @@
         <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-1.50382873160811e-05</v>
+        <v>0.01102769443772663</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
       </c>
       <c r="FS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.002937896110566618</v>
+        <v>-0.007419870219579912</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.04561278709279139</v>
+        <v>-0.0777873184244183</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.002126888166033868</v>
+        <v>-0.0281691887905712</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.04145732581334896</v>
+        <v>0.1756890438874273</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -6115,7 +6115,7 @@
         <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.4944175880602533</v>
+        <v>0.3673263660664046</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -6132,16 +6132,16 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1198894349094563</v>
+        <v>-0.03132362115763966</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4544460008606231</v>
+        <v>-0.1574310961824845</v>
       </c>
       <c r="G11" t="n">
         <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4274607518904434</v>
+        <v>0.4485034714310024</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,25 +6159,25 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.04888874850773579</v>
+        <v>-0.130178196493785</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4157528138401824</v>
+        <v>-0.1955038102499164</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.04063933094066322</v>
+        <v>0.1181387580374067</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,16 +6186,16 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.08967454752124288</v>
+        <v>-0.1505967697670783</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.01598316809495008</v>
+        <v>-0.008656607559602366</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,19 +6204,19 @@
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.02252847513618931</v>
+        <v>-0.03162450802245122</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.008390708569729568</v>
+        <v>-0.2887825223557907</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.03544500394326719</v>
+        <v>0.003527479040623809</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.08318877872611036</v>
+        <v>0.04767021123248868</v>
       </c>
       <c r="AM11" t="n">
         <v>-0</v>
@@ -6240,10 +6240,10 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.0007077278191615895</v>
+        <v>-0.05554508401760289</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.08540701532056351</v>
+        <v>0.01816034171727798</v>
       </c>
       <c r="AQ11" t="n">
         <v>-0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.4218259438604975</v>
+        <v>0.5191454181042116</v>
       </c>
       <c r="AV11" t="n">
         <v>-0</v>
@@ -6267,16 +6267,16 @@
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.06897385573744649</v>
+        <v>-0.2773316772019603</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.2205919160920708</v>
+        <v>-0.1188790333326577</v>
       </c>
       <c r="AZ11" t="n">
         <v>-0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.1099878069610339</v>
+        <v>-0.04339056641769333</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
@@ -6294,52 +6294,52 @@
         <v>0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1555668212240102</v>
+        <v>-0.02496902837454742</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.2031233903851091</v>
+        <v>-0.08294885925804485</v>
       </c>
       <c r="BI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.1451342674025795</v>
+        <v>0.05824419041574769</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>-0.002556688646453596</v>
+        <v>0.08937834520485273</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.0211355153587851</v>
+        <v>-0.02766133106619291</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.2207219932939731</v>
+        <v>0.280554085961145</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,10 +6348,10 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.06717633274302381</v>
+        <v>-0.08484454530252006</v>
       </c>
       <c r="BZ11" t="n">
-        <v>-0.129854641674758</v>
+        <v>-0.1133443628907627</v>
       </c>
       <c r="CA11" t="n">
         <v>-0</v>
@@ -6366,22 +6366,22 @@
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.08697241061607046</v>
+        <v>-0.1241005857088528</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
         <v>-0</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.005260933946613045</v>
+        <v>0.02982513345676222</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.1102993405917673</v>
+        <v>0.05788680263723674</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,49 +6393,49 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-4.43257607350541e-05</v>
+        <v>-0.1130418455220918</v>
       </c>
       <c r="CO11" t="n">
         <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.01466065102031537</v>
+        <v>0.1111120639927183</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.02412898156694127</v>
+        <v>0.09855759559282742</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV11" t="n">
         <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.0687753690642883</v>
+        <v>-0.1207477986492186</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.001385798239291539</v>
+        <v>0.00912079538591205</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.1157981227674384</v>
+        <v>0.0813693175712514</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6447,25 +6447,25 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.04431739291869521</v>
+        <v>-0.0540124289549061</v>
       </c>
       <c r="DG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0469190519338525</v>
+        <v>-0.1975404969883628</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0004228659813447472</v>
+        <v>0.07982109192302066</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM11" t="n">
         <v>0</v>
@@ -6474,19 +6474,19 @@
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.006641109162840441</v>
+        <v>-0.02073396924641933</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.03409219115504388</v>
+        <v>-0.06329309576383095</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.007839961212285225</v>
+        <v>0.08041025222081968</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6495,13 +6495,13 @@
         <v>-0</v>
       </c>
       <c r="DV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.05630551712360807</v>
+        <v>-0.0268568656386304</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,25 +6510,25 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.01739268735557954</v>
+        <v>-0.0550253324327012</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.05349210144062201</v>
+        <v>0.04359670920676496</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
         <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.1002099334802206</v>
+        <v>-0.05013198736437276</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
@@ -6537,79 +6537,79 @@
         <v>-0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.02829821554655291</v>
+        <v>0.01336142295899115</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.1234794527568776</v>
+        <v>-0.006961048616991997</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
         <v>-0</v>
       </c>
       <c r="EN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO11" t="n">
         <v>0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.03354367535041377</v>
+        <v>-0.01249802592186753</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>-0</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.01138240262551658</v>
+        <v>-0.005899383144940205</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.07389758701291133</v>
+        <v>0.1446168996258657</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
         <v>0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.06650577815978947</v>
+        <v>-0.1419693449424611</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
         <v>-0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.00686835868898876</v>
+        <v>-0.0004515334052908549</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.1058259541203652</v>
+        <v>0.04850484575129888</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG11" t="n">
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.005797606991718213</v>
+        <v>0.2021335913128045</v>
       </c>
       <c r="FI11" t="n">
         <v>-0</v>
@@ -6618,16 +6618,16 @@
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.008269053209006944</v>
+        <v>-0.07289011355661995</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.05044232467575337</v>
+        <v>0.1309518990581542</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,46 +6636,46 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.005420703803291718</v>
+        <v>0.008538417899239708</v>
       </c>
       <c r="FR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS11" t="n">
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.008628367138022312</v>
+        <v>-0.02237659527608413</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.03001674149327355</v>
+        <v>-0.04848437542451323</v>
       </c>
       <c r="FV11" t="n">
         <v>-0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.04279250744070507</v>
+        <v>-0.03346134264582198</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.05313188342164341</v>
+        <v>0.08115448268945702</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6684,7 +6684,7 @@
         <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.1465852228526663</v>
+        <v>0.3969256418546411</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -7839,25 +7839,25 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.07399542798630397</v>
+        <v>-0.01718061647502239</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0709790340585276</v>
+        <v>-0.1595186744597766</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1108856173884611</v>
+        <v>0.4372282952607412</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7866,25 +7866,25 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.04595669083434802</v>
+        <v>-0.1139331941005722</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.06470193804116534</v>
+        <v>-0.1912269917031652</v>
       </c>
       <c r="P14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.01286623979709052</v>
+        <v>0.1044942959889899</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -7893,40 +7893,40 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.006100835549428585</v>
+        <v>-0.09466072415932646</v>
       </c>
       <c r="X14" t="n">
-        <v>0.009342836230473214</v>
+        <v>-0.02024099506776598</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>-0.004928984544738137</v>
+        <v>-0.03685664010370459</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.01258156439247423</v>
+        <v>-0.2552359378293638</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.01050107998378377</v>
+        <v>0.045977414084051</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI14" t="n">
         <v>-0</v>
@@ -7938,22 +7938,22 @@
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.009158633067053728</v>
+        <v>0.04261947115897059</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.009344143710511673</v>
+        <v>-0.03674726705645801</v>
       </c>
       <c r="AP14" t="n">
-        <v>-0.01452169277157193</v>
+        <v>0.004084694325702766</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR14" t="n">
         <v>-0</v>
@@ -7962,28 +7962,28 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.1019198328055797</v>
+        <v>0.4298116403776999</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>-0.02807047747016878</v>
+        <v>-0.266703631100383</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0.02016552463268135</v>
+        <v>-0.1209157629426972</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>0</v>
@@ -7992,7 +7992,7 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.03040979956368515</v>
+        <v>-0.01793593956142691</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
@@ -8001,52 +8001,52 @@
         <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.05200338909831748</v>
+        <v>-0.006101564241852741</v>
       </c>
       <c r="BH14" t="n">
-        <v>-0.06011200255662029</v>
+        <v>-0.06069118740482153</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.03426528983123459</v>
+        <v>0.05052678002126591</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.01557273011220122</v>
+        <v>0.06157330246901688</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.01534036555480199</v>
+        <v>-0.01112595399125816</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.047368182566852</v>
+        <v>0.2414822798158145</v>
       </c>
       <c r="BW14" t="n">
         <v>0</v>
@@ -8055,10 +8055,10 @@
         <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>-0.01165554142871243</v>
+        <v>-0.05985773466473071</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0.01167342535910132</v>
+        <v>-0.1240202384482711</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
@@ -8070,28 +8070,28 @@
         <v>-0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.02434920044063748</v>
+        <v>-0.1137540148714066</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.006277110844750866</v>
+        <v>0.02917904079566028</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.01747917093761229</v>
+        <v>0.05963678913299981</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
         <v>0</v>
@@ -8100,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.0008711438210970087</v>
+        <v>-0.1147816444000389</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
@@ -8109,97 +8109,97 @@
         <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.004870258777359961</v>
+        <v>0.1496826747591614</v>
       </c>
       <c r="CR14" t="n">
-        <v>-0.01055356244104783</v>
+        <v>0.06868932225718427</v>
       </c>
       <c r="CS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT14" t="n">
         <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>-0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.01837875031968109</v>
+        <v>-0.1119537330061609</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.005788378002291633</v>
+        <v>0.01827083508161986</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.01825785415799794</v>
+        <v>0.08222235311554203</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.03055706956215015</v>
+        <v>-0.07805895886511502</v>
       </c>
       <c r="DG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.04795676047248516</v>
+        <v>-0.2053762820890815</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.01313787130993649</v>
+        <v>0.06667956780340208</v>
       </c>
       <c r="DK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL14" t="n">
         <v>-0</v>
       </c>
       <c r="DM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.004916013979101529</v>
+        <v>-0.009997958543084565</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
         <v>0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.01919661233951572</v>
+        <v>-0.06021135600141588</v>
       </c>
       <c r="DS14" t="n">
-        <v>-0.007774198957988798</v>
+        <v>0.04169724196238191</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>-0</v>
@@ -8208,49 +8208,49 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.02846097191678534</v>
+        <v>-0.005631911990851824</v>
       </c>
       <c r="DY14" t="n">
         <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01360604075316584</v>
+        <v>-0.03638945139055259</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.01789462456361692</v>
+        <v>0.01366938329681499</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.02911864151567194</v>
+        <v>-0.05787979272810461</v>
       </c>
       <c r="EH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.008480714679931127</v>
+        <v>0.01772311591468043</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.01387669463880132</v>
+        <v>0.002135051693077886</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>-0</v>
@@ -8259,22 +8259,22 @@
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.01260822431150292</v>
+        <v>-0.03440564933223574</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.003845554478425642</v>
+        <v>-0.01208967426754717</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0.01036215508293767</v>
+        <v>0.1090035198219108</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
@@ -8283,58 +8283,58 @@
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.01930000018848992</v>
+        <v>-0.1301528791426035</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.008683513147103507</v>
+        <v>0.002589470299987057</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.02122334911163535</v>
+        <v>0.04926107642619053</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>-0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.01604457638516874</v>
+        <v>0.1839387303034509</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.01197799151554985</v>
+        <v>-0.07780575109705781</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.01949669269291303</v>
+        <v>0.1383156177246908</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
         <v>0</v>
@@ -8343,78 +8343,78 @@
         <v>0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.0001186836000044023</v>
+        <v>0.002269034342212356</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.001333692896077636</v>
+        <v>-0.009107064464106952</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0182015524807463</v>
+        <v>-0.03162385840654541</v>
       </c>
       <c r="FV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.0001952809621877177</v>
+        <v>-0.040712622699525</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
         <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0.00411468136418883</v>
+        <v>0.0758062636767521</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
         <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-0.8502837428435279</v>
+        <v>-0.2632674171497739</v>
       </c>
       <c r="B15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.05655871633976203</v>
+        <v>0.209488579268205</v>
       </c>
       <c r="F15" t="n">
-        <v>1.687231382981478</v>
+        <v>0.6283093612791977</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -8423,22 +8423,22 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.4323332666266763</v>
+        <v>-0.16441393391849</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1602354216972428</v>
+        <v>0.3905909750829961</v>
       </c>
       <c r="O15" t="n">
-        <v>1.278894506970289</v>
+        <v>1.067381410106608</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
@@ -8450,52 +8450,52 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1922866802710226</v>
+        <v>0.08536340758348407</v>
       </c>
       <c r="T15" t="n">
         <v>-0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V15" t="n">
         <v>-0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5082619239813235</v>
+        <v>-0.02150163681497325</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1915377317545275</v>
+        <v>0.128464423379295</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>-0.2231365369000803</v>
+        <v>-0.1540701535566233</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>-0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.1062409241909324</v>
+        <v>0.02410445369008753</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.09126751785465746</v>
+        <v>-0.3189598640268801</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
@@ -8504,7 +8504,7 @@
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0.1899579490643113</v>
+        <v>-0.08704243343982818</v>
       </c>
       <c r="AL15" t="n">
         <v>-0</v>
@@ -8516,10 +8516,10 @@
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.01888882982903044</v>
+        <v>-0.3521654900326996</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.06123801101473281</v>
+        <v>-0.02474078680267843</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -8528,52 +8528,52 @@
         <v>-0</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0.6097803001632807</v>
+        <v>-0.02157083022841234</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.6201411756746733</v>
+        <v>-0.2630871735945537</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.052831566551708</v>
+        <v>0.6539432702725795</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>-0.2060866365751479</v>
+        <v>-0.1945146997898888</v>
       </c>
       <c r="BD15" t="n">
         <v>-0</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1354846950335468</v>
+        <v>0.5691703431710214</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.1952686044250534</v>
+        <v>-0.3498127435036994</v>
       </c>
       <c r="BI15" t="n">
         <v>-0</v>
@@ -8585,10 +8585,10 @@
         <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0.03870840396197738</v>
+        <v>0.1527822424762326</v>
       </c>
       <c r="BM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
@@ -8597,40 +8597,40 @@
         <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.06466038365058653</v>
+        <v>0.03445941759659151</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.1143795097060027</v>
+        <v>0.02567225477356964</v>
       </c>
       <c r="BR15" t="n">
         <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT15" t="n">
         <v>-0</v>
       </c>
       <c r="BU15" t="n">
-        <v>-0.4089227988679115</v>
+        <v>-0.01203677852762843</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.3257989605731144</v>
+        <v>-0.04024737753969684</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.6145798994091752</v>
+        <v>0.3525289303833425</v>
       </c>
       <c r="CA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="n">
         <v>-0</v>
@@ -8639,7 +8639,7 @@
         <v>-0</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.2339331298305126</v>
+        <v>0.07345054580648686</v>
       </c>
       <c r="CE15" t="n">
         <v>-0</v>
@@ -8651,22 +8651,22 @@
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.03677137526617377</v>
+        <v>-0.04725116843565927</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0.3353032623842591</v>
+        <v>-0.06039160539440133</v>
       </c>
       <c r="CJ15" t="n">
         <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL15" t="n">
         <v>-0</v>
       </c>
       <c r="CM15" t="n">
-        <v>-0.01918928072767162</v>
+        <v>-0.0775998314595973</v>
       </c>
       <c r="CN15" t="n">
         <v>0</v>
@@ -8678,25 +8678,25 @@
         <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.5706829987925043</v>
+        <v>-0.19300799013398</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.08236883473748149</v>
+        <v>0.270372402189268</v>
       </c>
       <c r="CS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.2203005068442297</v>
+        <v>0.08847749042046107</v>
       </c>
       <c r="CW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX15" t="n">
         <v>-0</v>
@@ -8705,10 +8705,10 @@
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.03393527105203356</v>
+        <v>-0.1431402407705024</v>
       </c>
       <c r="DA15" t="n">
-        <v>-0.3184503568692622</v>
+        <v>-0.1493073813460601</v>
       </c>
       <c r="DB15" t="n">
         <v>0</v>
@@ -8717,64 +8717,64 @@
         <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE15" t="n">
-        <v>-0.001021463966942377</v>
+        <v>0.005702698874129549</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.4784050070619013</v>
+        <v>0.1655221300707579</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0.04168057656363482</v>
+        <v>-0.1487924714087882</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.1183995626040507</v>
+        <v>0.02059958295346414</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DP15" t="n">
         <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.1265712080371372</v>
+        <v>0.1345543001457302</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0.09133203575488023</v>
+        <v>-0.1932710553984657</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.05651170388601569</v>
+        <v>0.06870129930356661</v>
       </c>
       <c r="DX15" t="n">
         <v>-0</v>
@@ -8783,43 +8783,43 @@
         <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.02092785148218939</v>
+        <v>-0.1085888242326713</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0.4458962471348428</v>
+        <v>-0.2807577804850698</v>
       </c>
       <c r="EC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED15" t="n">
         <v>-0</v>
       </c>
       <c r="EE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.150650987458159</v>
+        <v>-0.05828302996004474</v>
       </c>
       <c r="EG15" t="n">
         <v>-0</v>
       </c>
       <c r="EH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI15" t="n">
         <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.1534375046047704</v>
+        <v>-0.1747669799486979</v>
       </c>
       <c r="EK15" t="n">
-        <v>-0.2033266677291174</v>
+        <v>-0.06677483701364652</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
@@ -8828,7 +8828,7 @@
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.08454460904624655</v>
+        <v>0.02145072903661248</v>
       </c>
       <c r="EP15" t="n">
         <v>-0</v>
@@ -8840,10 +8840,10 @@
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.3250134762032604</v>
+        <v>-0.09520561870017522</v>
       </c>
       <c r="ET15" t="n">
-        <v>-0.06627756881633352</v>
+        <v>-0.1823384893688573</v>
       </c>
       <c r="EU15" t="n">
         <v>-0</v>
@@ -8852,10 +8852,10 @@
         <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.187822665324337</v>
+        <v>0.04976585726261427</v>
       </c>
       <c r="EY15" t="n">
         <v>-0</v>
@@ -8867,94 +8867,94 @@
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.08804884683926674</v>
+        <v>-0.04071157965018422</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0.2809320706643329</v>
+        <v>-0.1488192175556596</v>
       </c>
       <c r="FD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>-0.09838211950112487</v>
+        <v>-0.1582405464879239</v>
       </c>
       <c r="FH15" t="n">
         <v>0</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.08654835641166246</v>
+        <v>-0.06669776593887092</v>
       </c>
       <c r="FL15" t="n">
-        <v>-0.003487209481427227</v>
+        <v>-0.2664089717302998</v>
       </c>
       <c r="FM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.02852771258249955</v>
+        <v>0.02585028793104953</v>
       </c>
       <c r="FQ15" t="n">
         <v>0</v>
       </c>
       <c r="FR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS15" t="n">
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.004379587628498551</v>
+        <v>0.001954674052398164</v>
       </c>
       <c r="FU15" t="n">
-        <v>-0.3123973185146371</v>
+        <v>-0.09633217170277589</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX15" t="n">
         <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0.09610245220745987</v>
+        <v>-0.1617989115940726</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.05448303746657592</v>
+        <v>-0.09756517395285559</v>
       </c>
       <c r="GE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF15" t="n">
         <v>-0</v>
